--- a/data/ams_weekly_data/Nexlev/ads_report_week29.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week29.xlsx
@@ -1994,10 +1994,10 @@
         <v>81801</v>
       </c>
       <c r="G56" t="n">
-        <v>7454.24</v>
+        <v>5590.68</v>
       </c>
       <c r="H56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3086,10 +3086,10 @@
         <v>222852</v>
       </c>
       <c r="G95" t="n">
-        <v>142604.14</v>
+        <v>145569.39</v>
       </c>
       <c r="H95" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="96">
@@ -3394,10 +3394,10 @@
         <v>78753</v>
       </c>
       <c r="G106" t="n">
-        <v>101686.4</v>
+        <v>111855.04</v>
       </c>
       <c r="H106" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107">
@@ -6278,10 +6278,10 @@
         <v>37967</v>
       </c>
       <c r="G209" t="n">
-        <v>16268.64</v>
+        <v>21691.52</v>
       </c>
       <c r="H209" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="210">
